--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136343000</v>
       </c>
       <c r="B66" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>136343050</v>
       </c>
       <c r="B67" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136343000</v>
       </c>
       <c r="B66" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>136343050</v>
       </c>
       <c r="B67" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136342841</v>
       </c>
       <c r="B10" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136341087</v>
       </c>
       <c r="B18" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>136342806</v>
       </c>
       <c r="B19" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>136342819</v>
       </c>
       <c r="B20" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136342835</v>
       </c>
       <c r="B21" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>136343068</v>
       </c>
       <c r="B22" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>136343137</v>
       </c>
       <c r="B23" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>136343238</v>
       </c>
       <c r="B24" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136343301</v>
       </c>
       <c r="B25" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>136343335</v>
       </c>
       <c r="B26" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136343307</v>
       </c>
       <c r="B28" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136341289</v>
       </c>
       <c r="B29" t="n">
-        <v>58019</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>136342854</v>
       </c>
       <c r="B32" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>136340912</v>
       </c>
       <c r="B42" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>136341011</v>
       </c>
       <c r="B43" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>136341119</v>
       </c>
       <c r="B44" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>136341357</v>
       </c>
       <c r="B45" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>136341429</v>
       </c>
       <c r="B46" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136341497</v>
       </c>
       <c r="B47" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>136341523</v>
       </c>
       <c r="B48" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>136341543</v>
       </c>
       <c r="B49" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>136341560</v>
       </c>
       <c r="B50" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>136341581</v>
       </c>
       <c r="B51" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>136341622</v>
       </c>
       <c r="B52" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136341629</v>
       </c>
       <c r="B53" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>136341667</v>
       </c>
       <c r="B54" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>136342956</v>
       </c>
       <c r="B55" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>136342980</v>
       </c>
       <c r="B56" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136343099</v>
       </c>
       <c r="B57" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136343172</v>
       </c>
       <c r="B58" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>136343199</v>
       </c>
       <c r="B59" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>136343218</v>
       </c>
       <c r="B60" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>136343251</v>
       </c>
       <c r="B61" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>136343282</v>
       </c>
       <c r="B62" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136343328</v>
       </c>
       <c r="B63" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136343343</v>
       </c>
       <c r="B64" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>136343375</v>
       </c>
       <c r="B65" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136343000</v>
       </c>
       <c r="B66" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>136343050</v>
       </c>
       <c r="B67" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136343000</v>
       </c>
       <c r="B66" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>136343050</v>
       </c>
       <c r="B67" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136342841</v>
       </c>
       <c r="B10" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136341087</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>136342806</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>136342819</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136342835</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>136343068</v>
       </c>
       <c r="B22" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>136343137</v>
       </c>
       <c r="B23" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>136343238</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136343301</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>136343335</v>
       </c>
       <c r="B26" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136343307</v>
       </c>
       <c r="B28" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136343000</v>
       </c>
       <c r="B66" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>136343050</v>
       </c>
       <c r="B67" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136342841</v>
       </c>
       <c r="B10" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136341087</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>136342806</v>
       </c>
       <c r="B19" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>136342819</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136342835</v>
       </c>
       <c r="B21" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>136343068</v>
       </c>
       <c r="B22" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>136343137</v>
       </c>
       <c r="B23" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>136343238</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136343301</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>136343335</v>
       </c>
       <c r="B26" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136343307</v>
       </c>
       <c r="B28" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136343000</v>
       </c>
       <c r="B66" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>136343050</v>
       </c>
       <c r="B67" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
